--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_basbrut_a_2023.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_basbrut_a_2023.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:47</t>
+    <t xml:space="preserve">2026-09-24 01:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -707,7 +707,7 @@
         <v>22</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.07</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>328</v>
@@ -721,7 +721,7 @@
         <v>22</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.38</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>328</v>
@@ -735,7 +735,7 @@
         <v>22</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>328</v>
